--- a/analysis/tables/ours-13b.xlsx
+++ b/analysis/tables/ours-13b.xlsx
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.489679033322039</v>
+        <v>0.4898371300807023</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05416725219321766</v>
+        <v>0.05406152926198543</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6610195239634022</v>
+        <v>0.6611963467765015</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08584886838709019</v>
+        <v>0.08584497590277905</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.110617871109859</v>
+        <v>-0.1103663359555422</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5438462855152567</v>
+        <v>0.5438986593426878</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2254935800903592</v>
+        <v>0.2254761055634857</v>
       </c>
     </row>
     <row r="3">
@@ -536,30 +536,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7955985759001127</v>
+        <v>0.8461232220523061</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.04188786549879653</v>
+        <v>-0.2285482935813685</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.796x - 0.042</t>
+          <t>y = 0.846x - 0.229</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8164806074401034</v>
+        <v>0.8074786585497478</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07688491321267643</v>
+        <v>0.07673681612953624</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05264949783426402</v>
+        <v>0.2701123047149271</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7537107104013162</v>
+        <v>0.6175749284709375</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2254935800903592</v>
+        <v>0.2254761055634857</v>
       </c>
     </row>
     <row r="4">
@@ -577,30 +577,30 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7957699178953539</v>
+        <v>0.8365964256503772</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02455020241324579</v>
+        <v>-0.2163335723841607</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.796x - 0.025</t>
+          <t>y = 0.837x - 0.216</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8200198151017841</v>
+        <v>0.8095381824244459</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07674293204164766</v>
+        <v>0.07665339260463401</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03085088021192857</v>
+        <v>0.2585877320907523</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7712197154821081</v>
+        <v>0.6202628532662164</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2254935800903592</v>
+        <v>0.2254761055634857</v>
       </c>
     </row>
   </sheetData>
